--- a/data/transactions_by_category.xlsx
+++ b/data/transactions_by_category.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">436,486</t>
   </si>
   <si>
-    <t xml:space="preserve">514,312</t>
+    <t xml:space="preserve">359,312</t>
   </si>
   <si>
     <t xml:space="preserve">343,384</t>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">210,180</t>
   </si>
   <si>
-    <t xml:space="preserve">170,620</t>
+    <t xml:space="preserve">248,120</t>
   </si>
   <si>
     <t xml:space="preserve">204,864</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">44,800</t>
   </si>
   <si>
-    <t xml:space="preserve">305,308</t>
+    <t xml:space="preserve">72,808</t>
   </si>
   <si>
     <t xml:space="preserve">38,100</t>
@@ -381,7 +381,7 @@
     <t xml:space="preserve">92,251</t>
   </si>
   <si>
-    <t xml:space="preserve">-149,788</t>
+    <t xml:space="preserve">5,212</t>
   </si>
   <si>
     <t xml:space="preserve">9,303</t>
@@ -429,7 +429,7 @@
     <t xml:space="preserve">17%    </t>
   </si>
   <si>
-    <t xml:space="preserve">-41%   </t>
+    <t xml:space="preserve">1%     </t>
   </si>
   <si>
     <t xml:space="preserve">55%    </t>
@@ -829,6 +829,12 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Manually added rent and deposit to replace atm cash withdrawals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cathy</t>
+  </si>
+  <si>
     <t xml:space="preserve">電子轉出 房租 (007)0000010668132820
 </t>
   </si>
@@ -990,42 +996,6 @@
   <si>
     <t xml:space="preserve">電子轉出 ｃｌｅａｎｉｎｇ　 (700)0000013131001632
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 82204957068FE5F60E −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 82204957068FE5F4D5 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 82204957068FE5F36C −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 82204957068FE5F1F9 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 82204957068FE5F077 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24028933 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24028719 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24028554 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24028357 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24027938 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24027825 −</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨行提款 007007094R24027709 −</t>
   </si>
   <si>
     <t xml:space="preserve">跨行提款 005005090120789063 −</t>
@@ -2586,7 +2556,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -2653,7 +2623,7 @@
         <v>45850</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-50000</v>
@@ -2666,7 +2636,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2682,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
@@ -2690,7 +2660,7 @@
         <v>45850</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-50000</v>
@@ -2703,7 +2673,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -2719,7 +2689,7 @@
         <v>8</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4">
@@ -2727,7 +2697,7 @@
         <v>45851</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-50000</v>
@@ -2736,11 +2706,11 @@
         <v>153</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -2756,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5">
@@ -2764,7 +2734,7 @@
         <v>45859</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-440</v>
@@ -2777,7 +2747,7 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -2793,7 +2763,7 @@
         <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6">
@@ -2801,7 +2771,7 @@
         <v>45870</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-50000</v>
@@ -2810,11 +2780,11 @@
         <v>153</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -2830,7 +2800,7 @@
         <v>9</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -2838,7 +2808,7 @@
         <v>45884</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-40000</v>
@@ -2851,7 +2821,7 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -2867,7 +2837,7 @@
         <v>9</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8">
@@ -2875,7 +2845,7 @@
         <v>45884</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-50000</v>
@@ -2888,7 +2858,7 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -2904,7 +2874,7 @@
         <v>9</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -2912,7 +2882,7 @@
         <v>45901</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-50000</v>
@@ -2921,11 +2891,11 @@
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -2941,7 +2911,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -2949,7 +2919,7 @@
         <v>45912</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-50000</v>
@@ -2962,7 +2932,7 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2978,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11">
@@ -2986,7 +2956,7 @@
         <v>45912</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>-50000</v>
@@ -2999,7 +2969,7 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3015,7 +2985,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12">
@@ -3023,7 +2993,7 @@
         <v>45967</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>-49000</v>
@@ -3036,7 +3006,7 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3052,7 +3022,7 @@
         <v>12</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13">
@@ -3060,7 +3030,7 @@
         <v>45967</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>-50000</v>
@@ -3073,7 +3043,7 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -3089,7 +3059,7 @@
         <v>12</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14">
@@ -3097,7 +3067,7 @@
         <v>46025</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>-50000</v>
@@ -3110,7 +3080,7 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -3126,7 +3096,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15">
@@ -3134,7 +3104,7 @@
         <v>46054</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>-50000</v>
@@ -3147,7 +3117,7 @@
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -3163,7 +3133,7 @@
         <v>15</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16">
@@ -3171,7 +3141,7 @@
         <v>46055</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>-39794</v>
@@ -3184,7 +3154,7 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -3200,7 +3170,7 @@
         <v>15</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +3186,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -3296,7 +3266,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3312,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3">
@@ -3320,7 +3290,7 @@
         <v>45656</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-50000</v>
@@ -3333,7 +3303,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3349,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
@@ -3357,7 +3327,7 @@
         <v>45709</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-24600</v>
@@ -3370,7 +3340,7 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -3386,7 +3356,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5">
@@ -3394,7 +3364,7 @@
         <v>45968</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-10000</v>
@@ -3405,7 +3375,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -3421,7 +3391,42 @@
         <v>12</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-155000</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -3437,7 +3442,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -6289,7 +6294,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -8604,20 +8609,18 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>45977</v>
+        <v>45975</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>248</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>-20000</v>
+        <v>-77500</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>246</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
         <v>197</v>
@@ -8641,19 +8644,19 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>45982</v>
+        <v>45977</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>-32000</v>
+        <v>-20000</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
@@ -8681,16 +8684,16 @@
         <v>45982</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>-29560</v>
+        <v>-32000</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
@@ -8715,19 +8718,19 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>45992</v>
+        <v>45982</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>-29000</v>
+        <v>-29560</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
@@ -8738,13 +8741,13 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>197</v>
@@ -8755,16 +8758,16 @@
         <v>45992</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>-32560</v>
+        <v>-29000</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
@@ -8789,13 +8792,13 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>-1000</v>
+        <v>-32560</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>153</v>
@@ -8826,19 +8829,19 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45997</v>
+        <v>45993</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>-27560</v>
+        <v>-1000</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
@@ -8863,18 +8866,20 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46000</v>
+        <v>45997</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>-18400</v>
+        <v>-27560</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E70" s="1"/>
+      <c r="E70" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
         <v>197</v>
@@ -8898,20 +8903,18 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>-20000</v>
+        <v>-18400</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>246</v>
-      </c>
+      <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1" t="s">
         <v>197</v>
@@ -8938,16 +8941,16 @@
         <v>46006</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>-36500</v>
+        <v>-20000</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
@@ -8978,13 +8981,13 @@
         <v>254</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>-31500</v>
+        <v>-36500</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
@@ -9009,19 +9012,19 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>-29560</v>
+        <v>-31500</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
@@ -9046,21 +9049,21 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>61210</v>
+        <v>-29560</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="E75" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
         <v>197</v>
       </c>
@@ -9083,21 +9086,21 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46020</v>
+        <v>46014</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>-32000</v>
+        <v>61210</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="G76" s="1" t="s">
         <v>197</v>
       </c>
@@ -9120,18 +9123,20 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>-7994</v>
+        <v>-32000</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E77" s="1"/>
+      <c r="E77" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
         <v>197</v>
@@ -9155,20 +9160,18 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>-29000</v>
+        <v>-7994</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>208</v>
-      </c>
+      <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
         <v>197</v>
@@ -9178,13 +9181,13 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>197</v>
@@ -9195,16 +9198,16 @@
         <v>46024</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>-32560</v>
+        <v>-29000</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
@@ -9229,19 +9232,19 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>-27560</v>
+        <v>-32560</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
@@ -9266,19 +9269,19 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>-1000</v>
+        <v>-27560</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
@@ -9303,19 +9306,19 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46037</v>
+        <v>46033</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>-31500</v>
+        <v>-1000</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
@@ -9343,16 +9346,16 @@
         <v>46037</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>-20000</v>
+        <v>-31500</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
@@ -9377,19 +9380,19 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46047</v>
+        <v>46037</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>-30000</v>
+        <v>-20000</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
@@ -9417,16 +9420,16 @@
         <v>46047</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>-32000</v>
+        <v>-30000</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="1" t="s">
@@ -9454,16 +9457,16 @@
         <v>46047</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>-29560</v>
+        <v>-32000</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
@@ -9488,19 +9491,19 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46054</v>
+        <v>46047</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>-29000</v>
+        <v>-29560</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
@@ -9511,13 +9514,13 @@
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M87" s="1" t="n">
         <v>2026</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>197</v>
@@ -9528,16 +9531,16 @@
         <v>46054</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>-32560</v>
+        <v>-29000</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
@@ -9562,13 +9565,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46059</v>
+        <v>46054</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>-1000</v>
+        <v>-32560</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>153</v>
@@ -9599,18 +9602,20 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>-2940</v>
+        <v>-1000</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E90" s="1"/>
+      <c r="E90" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1" t="s">
         <v>197</v>
@@ -9634,20 +9639,18 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>-27560</v>
+        <v>-2940</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>208</v>
-      </c>
+      <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
         <v>197</v>
@@ -9671,19 +9674,19 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46069</v>
+        <v>46062</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>-36500</v>
+        <v>-27560</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
@@ -9711,16 +9714,16 @@
         <v>46069</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>-31500</v>
+        <v>-36500</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1" t="s">
@@ -9748,16 +9751,16 @@
         <v>46069</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>-20000</v>
+        <v>-31500</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
@@ -9777,6 +9780,43 @@
         <v>15</v>
       </c>
       <c r="O94" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>197</v>
       </c>
     </row>
@@ -9793,7 +9833,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -9860,7 +9900,7 @@
         <v>45648</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-4000</v>
@@ -9873,7 +9913,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -9889,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3">
@@ -9897,7 +9937,7 @@
         <v>45650</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-2500</v>
@@ -9906,11 +9946,11 @@
         <v>153</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -9926,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4">
@@ -9934,7 +9974,7 @@
         <v>45657</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-3000</v>
@@ -9947,7 +9987,7 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -9963,7 +10003,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
@@ -9971,7 +10011,7 @@
         <v>45671</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-10000</v>
@@ -9982,7 +10022,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -9998,7 +10038,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
@@ -10006,7 +10046,7 @@
         <v>45694</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-2000</v>
@@ -10019,7 +10059,7 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -10035,7 +10075,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
@@ -10043,7 +10083,7 @@
         <v>45702</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-1000</v>
@@ -10056,7 +10096,7 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -10072,7 +10112,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
@@ -10080,7 +10120,7 @@
         <v>45706</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-1500</v>
@@ -10089,11 +10129,11 @@
         <v>153</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -10109,7 +10149,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
@@ -10117,7 +10157,7 @@
         <v>45717</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-2400</v>
@@ -10126,11 +10166,11 @@
         <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -10146,7 +10186,7 @@
         <v>4</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -10154,7 +10194,7 @@
         <v>45744</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-15300</v>
@@ -10165,7 +10205,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -10181,7 +10221,7 @@
         <v>4</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -10189,7 +10229,7 @@
         <v>45749</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>-14500</v>
@@ -10200,7 +10240,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -10216,7 +10256,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12">
@@ -10224,7 +10264,7 @@
         <v>45775</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>-21300</v>
@@ -10235,7 +10275,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -10251,7 +10291,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13">
@@ -10259,7 +10299,7 @@
         <v>45798</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>-15000</v>
@@ -10270,7 +10310,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -10286,7 +10326,7 @@
         <v>6</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14">
@@ -10294,7 +10334,7 @@
         <v>45808</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>-10510</v>
@@ -10303,11 +10343,11 @@
         <v>153</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -10323,7 +10363,7 @@
         <v>6</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15">
@@ -10331,7 +10371,7 @@
         <v>45852</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>-10000</v>
@@ -10342,7 +10382,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -10358,7 +10398,7 @@
         <v>8</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">
@@ -10366,7 +10406,7 @@
         <v>45874</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>-17400</v>
@@ -10377,7 +10417,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -10393,7 +10433,7 @@
         <v>9</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17">
@@ -10401,7 +10441,7 @@
         <v>45884</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>-10000</v>
@@ -10412,7 +10452,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -10428,7 +10468,7 @@
         <v>9</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18">
@@ -10436,7 +10476,7 @@
         <v>45884</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>-10000</v>
@@ -10449,7 +10489,7 @@
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -10465,7 +10505,7 @@
         <v>9</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19">
@@ -10473,7 +10513,7 @@
         <v>45901</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>-25800</v>
@@ -10484,7 +10524,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -10500,7 +10540,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20">
@@ -10508,7 +10548,7 @@
         <v>45927</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>-19000</v>
@@ -10519,7 +10559,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -10535,7 +10575,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21">
@@ -10543,7 +10583,7 @@
         <v>45962</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>-17354</v>
@@ -10552,11 +10592,11 @@
         <v>153</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -10572,7 +10612,7 @@
         <v>12</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22">
@@ -10580,7 +10620,7 @@
         <v>45962</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>-17354</v>
@@ -10589,11 +10629,11 @@
         <v>153</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -10609,18 +10649,18 @@
         <v>12</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45974</v>
+        <v>45991</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>-20000</v>
+        <v>-18100</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>153</v>
@@ -10628,7 +10668,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -10644,15 +10684,15 @@
         <v>12</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45974</v>
+        <v>45991</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>-20000</v>
@@ -10663,7 +10703,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -10679,18 +10719,18 @@
         <v>12</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45974</v>
+        <v>46016</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>-20000</v>
+        <v>-38100</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>153</v>
@@ -10698,34 +10738,34 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45974</v>
+        <v>46038</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>-20000</v>
+        <v>-36500</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>153</v>
@@ -10733,34 +10773,34 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45974</v>
+        <v>46051</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>-20000</v>
+        <v>-35000</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>153</v>
@@ -10768,34 +10808,34 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45975</v>
+        <v>46055</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>-12500</v>
+        <v>-18000</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>153</v>
@@ -10803,31 +10843,31 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45975</v>
+        <v>46055</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>-20000</v>
@@ -10838,480 +10878,60 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45975</v>
+        <v>46058</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>-18100</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46016</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>-38100</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46038</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>-36500</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46051</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>-18000</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46058</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="M42" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -11327,7 +10947,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -11394,7 +11014,7 @@
         <v>45732</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-3926</v>
@@ -11407,7 +11027,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -11423,7 +11043,7 @@
         <v>4</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -11431,7 +11051,7 @@
         <v>45760</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-8592</v>
@@ -11444,7 +11064,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -11460,7 +11080,7 @@
         <v>5</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -11468,7 +11088,7 @@
         <v>45820</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-11365</v>
@@ -11481,7 +11101,7 @@
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -11497,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -11505,18 +11125,18 @@
         <v>45863</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-182</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2025</v>
@@ -11540,7 +11160,7 @@
         <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
@@ -11548,18 +11168,18 @@
         <v>45863</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-20859</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2025</v>
@@ -11583,7 +11203,7 @@
         <v>8</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
@@ -11591,18 +11211,18 @@
         <v>45903</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-792</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2025</v>
@@ -11626,7 +11246,7 @@
         <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -11634,18 +11254,18 @@
         <v>45945</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-2956</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2025</v>
@@ -11669,7 +11289,7 @@
         <v>11</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -11677,18 +11297,18 @@
         <v>45945</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-21725</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2025</v>
@@ -11712,7 +11332,7 @@
         <v>11</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -11720,18 +11340,18 @@
         <v>45948</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-2900</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2025</v>
@@ -11755,7 +11375,7 @@
         <v>11</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -11763,18 +11383,18 @@
         <v>45950</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>-608</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2025</v>
@@ -11798,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12">
@@ -11806,18 +11426,18 @@
         <v>45950</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>-750</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2025</v>
@@ -11841,7 +11461,7 @@
         <v>11</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -11849,18 +11469,18 @@
         <v>45950</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>-494</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>2025</v>
@@ -11884,7 +11504,7 @@
         <v>11</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14">
@@ -11892,18 +11512,18 @@
         <v>45950</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>-902</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>2025</v>
@@ -11927,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -11935,18 +11555,18 @@
         <v>45979</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>-3288</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>2025</v>
@@ -11970,7 +11590,7 @@
         <v>12</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
@@ -11978,18 +11598,18 @@
         <v>46017</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>-4142</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>2025</v>
@@ -12013,7 +11633,7 @@
         <v>13</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12021,18 +11641,18 @@
         <v>46017</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>-2625</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>2025</v>
@@ -12056,7 +11676,7 @@
         <v>13</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -12064,18 +11684,18 @@
         <v>46017</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>-4097</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>2025</v>
@@ -12099,7 +11719,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19">
@@ -12107,18 +11727,18 @@
         <v>46017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>-2096</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>2025</v>
@@ -12142,7 +11762,7 @@
         <v>13</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -12150,18 +11770,18 @@
         <v>46017</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>-4505</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>2025</v>
@@ -12185,7 +11805,7 @@
         <v>13</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21">
@@ -12193,18 +11813,18 @@
         <v>46024</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>-629</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>2026</v>
@@ -12228,7 +11848,7 @@
         <v>14</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22">
@@ -12236,18 +11856,18 @@
         <v>46029</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>-3337</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>2026</v>
@@ -12271,7 +11891,7 @@
         <v>14</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23">
@@ -12279,18 +11899,18 @@
         <v>46039</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>-5442</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>2026</v>
@@ -12314,7 +11934,7 @@
         <v>14</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24">
@@ -12322,18 +11942,18 @@
         <v>46055</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>-2697</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>2026</v>
@@ -12357,7 +11977,7 @@
         <v>15</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -12373,7 +11993,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -12440,7 +12060,7 @@
         <v>45803</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-2000</v>
@@ -12453,7 +12073,7 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -12469,7 +12089,7 @@
         <v>6</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -12477,18 +12097,18 @@
         <v>45931</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-3500</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2025</v>
@@ -12512,7 +12132,7 @@
         <v>11</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
@@ -12520,18 +12140,18 @@
         <v>45934</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-5600</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2025</v>
@@ -12555,7 +12175,7 @@
         <v>11</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -12563,18 +12183,18 @@
         <v>45951</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-3583</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2025</v>
@@ -12598,7 +12218,7 @@
         <v>11</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12234,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -12681,7 +12301,7 @@
         <v>45631</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-15</v>
@@ -12692,7 +12312,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -12716,7 +12336,7 @@
         <v>45631</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>-10600</v>
@@ -12729,7 +12349,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -12753,7 +12373,7 @@
         <v>45634</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>-15</v>
@@ -12764,7 +12384,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -12788,7 +12408,7 @@
         <v>45641</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-15</v>
@@ -12799,7 +12419,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -12823,7 +12443,7 @@
         <v>45641</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-8056</v>
@@ -12836,7 +12456,7 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -12860,7 +12480,7 @@
         <v>45641</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>-5000</v>
@@ -12871,7 +12491,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -12895,7 +12515,7 @@
         <v>45642</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-15</v>
@@ -12906,7 +12526,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -12930,7 +12550,7 @@
         <v>45642</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-1148</v>
@@ -12943,7 +12563,7 @@
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -12967,7 +12587,7 @@
         <v>45648</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-15</v>
@@ -12978,7 +12598,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -13002,7 +12622,7 @@
         <v>45648</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>-3665</v>
@@ -13015,7 +12635,7 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -13039,7 +12659,7 @@
         <v>45649</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>-600</v>
@@ -13048,11 +12668,11 @@
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -13076,7 +12696,7 @@
         <v>45649</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>-10</v>
@@ -13087,7 +12707,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -13111,7 +12731,7 @@
         <v>45649</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>-1000</v>
@@ -13122,7 +12742,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -13146,7 +12766,7 @@
         <v>45650</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>-15</v>
@@ -13157,7 +12777,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -13181,7 +12801,7 @@
         <v>45652</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>-15</v>
@@ -13192,7 +12812,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -13216,7 +12836,7 @@
         <v>45652</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>-12989</v>
@@ -13225,11 +12845,11 @@
         <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -13253,7 +12873,7 @@
         <v>45656</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>-15</v>
@@ -13264,7 +12884,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -13288,7 +12908,7 @@
         <v>45656</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>-18000</v>
@@ -13301,7 +12921,7 @@
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -13325,7 +12945,7 @@
         <v>45657</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>-15</v>
@@ -13336,7 +12956,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -13360,7 +12980,7 @@
         <v>45661</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>-15</v>
@@ -13371,7 +12991,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -13395,7 +13015,7 @@
         <v>45664</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>-15</v>
@@ -13406,7 +13026,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -13430,7 +13050,7 @@
         <v>45671</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>10000</v>
@@ -13443,7 +13063,7 @@
         <v>215</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -13467,7 +13087,7 @@
         <v>45673</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>-15</v>
@@ -13478,7 +13098,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -13502,7 +13122,7 @@
         <v>45674</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>1000</v>
@@ -13515,7 +13135,7 @@
         <v>215</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -13539,7 +13159,7 @@
         <v>45674</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>-5</v>
@@ -13550,7 +13170,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -13574,7 +13194,7 @@
         <v>45674</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>-1000</v>
@@ -13585,7 +13205,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -13609,7 +13229,7 @@
         <v>45680</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>-15</v>
@@ -13620,7 +13240,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -13644,7 +13264,7 @@
         <v>45680</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>-14617</v>
@@ -13657,7 +13277,7 @@
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -13681,7 +13301,7 @@
         <v>45684</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>-15</v>
@@ -13692,7 +13312,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -13716,7 +13336,7 @@
         <v>45684</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>-12000</v>
@@ -13727,7 +13347,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -13751,7 +13371,7 @@
         <v>45685</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>-15</v>
@@ -13762,7 +13382,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -13786,7 +13406,7 @@
         <v>45685</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>-10480</v>
@@ -13797,7 +13417,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -13821,7 +13441,7 @@
         <v>45692</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>-15</v>
@@ -13832,7 +13452,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -13856,7 +13476,7 @@
         <v>45694</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>-15</v>
@@ -13867,7 +13487,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -13891,7 +13511,7 @@
         <v>45696</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>-15</v>
@@ -13902,7 +13522,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -13926,7 +13546,7 @@
         <v>45696</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>-37098</v>
@@ -13939,7 +13559,7 @@
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -13963,7 +13583,7 @@
         <v>45696</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>-32912</v>
@@ -13972,11 +13592,11 @@
         <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -14000,7 +13620,7 @@
         <v>45699</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>-15</v>
@@ -14011,7 +13631,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -14035,7 +13655,7 @@
         <v>45699</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>-1900</v>
@@ -14046,7 +13666,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -14070,7 +13690,7 @@
         <v>45699</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>15</v>
@@ -14081,7 +13701,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -14105,7 +13725,7 @@
         <v>45699</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>-1900</v>
@@ -14116,7 +13736,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -14140,7 +13760,7 @@
         <v>45702</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>-15</v>
@@ -14151,7 +13771,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -14175,7 +13795,7 @@
         <v>45702</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>-10</v>
@@ -14186,7 +13806,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -14210,7 +13830,7 @@
         <v>45703</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>-15</v>
@@ -14221,7 +13841,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -14245,7 +13865,7 @@
         <v>45703</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>-14943</v>
@@ -14258,7 +13878,7 @@
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -14282,7 +13902,7 @@
         <v>45704</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>-15</v>
@@ -14293,7 +13913,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -14317,7 +13937,7 @@
         <v>45704</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>-1500</v>
@@ -14328,7 +13948,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -14352,7 +13972,7 @@
         <v>45705</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>-15</v>
@@ -14363,7 +13983,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -14387,7 +14007,7 @@
         <v>45705</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>-8000</v>
@@ -14400,7 +14020,7 @@
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -14424,7 +14044,7 @@
         <v>45706</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>-15</v>
@@ -14435,7 +14055,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -14459,7 +14079,7 @@
         <v>45706</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>-9999</v>
@@ -14470,7 +14090,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -14494,7 +14114,7 @@
         <v>45709</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>-15</v>
@@ -14505,7 +14125,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -14529,7 +14149,7 @@
         <v>45712</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>-6000</v>
@@ -14540,7 +14160,7 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -14564,7 +14184,7 @@
         <v>45717</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>-15</v>
@@ -14575,7 +14195,7 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -14599,7 +14219,7 @@
         <v>45718</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>-15</v>
@@ -14610,7 +14230,7 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -14634,7 +14254,7 @@
         <v>45720</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>-15</v>
@@ -14645,7 +14265,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -14669,7 +14289,7 @@
         <v>45723</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>-15</v>
@@ -14680,7 +14300,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -14704,7 +14324,7 @@
         <v>45724</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>-15</v>
@@ -14715,7 +14335,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -14739,7 +14359,7 @@
         <v>45724</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>-13780</v>
@@ -14752,7 +14372,7 @@
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -14776,7 +14396,7 @@
         <v>45725</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>-450</v>
@@ -14789,7 +14409,7 @@
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -14813,7 +14433,7 @@
         <v>45729</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>-500</v>
@@ -14826,7 +14446,7 @@
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -14850,7 +14470,7 @@
         <v>45730</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>-15</v>
@@ -14861,7 +14481,7 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -14885,7 +14505,7 @@
         <v>45730</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>-4850</v>
@@ -14896,7 +14516,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -14920,7 +14540,7 @@
         <v>45731</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>-15</v>
@@ -14931,7 +14551,7 @@
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -14955,7 +14575,7 @@
         <v>45731</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>-2500</v>
@@ -14966,7 +14586,7 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -14990,7 +14610,7 @@
         <v>45732</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>-15</v>
@@ -15001,7 +14621,7 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -15025,7 +14645,7 @@
         <v>45737</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>-15</v>
@@ -15036,7 +14656,7 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -15073,7 +14693,7 @@
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -15097,7 +14717,7 @@
         <v>45738</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>-15</v>
@@ -15108,7 +14728,7 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -15132,7 +14752,7 @@
         <v>45743</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>-15</v>
@@ -15143,7 +14763,7 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -15167,7 +14787,7 @@
         <v>45749</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>-15</v>
@@ -15178,7 +14798,7 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -15202,7 +14822,7 @@
         <v>45753</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>-500</v>
@@ -15215,7 +14835,7 @@
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -15239,7 +14859,7 @@
         <v>45753</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>-500</v>
@@ -15250,7 +14870,7 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -15274,7 +14894,7 @@
         <v>45753</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>-1000</v>
@@ -15285,7 +14905,7 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -15309,7 +14929,7 @@
         <v>45755</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>-15</v>
@@ -15320,7 +14940,7 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -15344,7 +14964,7 @@
         <v>45755</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>-4000</v>
@@ -15355,7 +14975,7 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -15379,7 +14999,7 @@
         <v>45758</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>-15</v>
@@ -15390,7 +15010,7 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -15414,7 +15034,7 @@
         <v>45760</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>-15</v>
@@ -15425,7 +15045,7 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -15449,7 +15069,7 @@
         <v>45760</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>-47387</v>
@@ -15462,7 +15082,7 @@
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -15486,7 +15106,7 @@
         <v>45760</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>-4000</v>
@@ -15499,7 +15119,7 @@
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -15523,7 +15143,7 @@
         <v>45761</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>-15</v>
@@ -15534,7 +15154,7 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -15558,7 +15178,7 @@
         <v>45761</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>-13730</v>
@@ -15567,11 +15187,11 @@
         <v>153</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -15608,7 +15228,7 @@
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -15632,7 +15252,7 @@
         <v>45762</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>-15</v>
@@ -15643,7 +15263,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -15667,7 +15287,7 @@
         <v>45762</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>-5000</v>
@@ -15680,7 +15300,7 @@
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -15704,7 +15324,7 @@
         <v>45767</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>-15</v>
@@ -15715,7 +15335,7 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -15739,7 +15359,7 @@
         <v>45768</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>-3900</v>
@@ -15750,7 +15370,7 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -15774,7 +15394,7 @@
         <v>45769</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>-15</v>
@@ -15785,7 +15405,7 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -15809,7 +15429,7 @@
         <v>45770</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>-10</v>
@@ -15820,7 +15440,7 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -15844,7 +15464,7 @@
         <v>45770</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>-1000</v>
@@ -15857,7 +15477,7 @@
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -15881,7 +15501,7 @@
         <v>45770</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>-15</v>
@@ -15892,7 +15512,7 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -15929,7 +15549,7 @@
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -15953,7 +15573,7 @@
         <v>45773</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>-1500</v>
@@ -15964,7 +15584,7 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -15988,7 +15608,7 @@
         <v>45774</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>-15</v>
@@ -15999,7 +15619,7 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -16023,7 +15643,7 @@
         <v>45774</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>-10</v>
@@ -16034,7 +15654,7 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -16058,7 +15678,7 @@
         <v>45774</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>-1000</v>
@@ -16071,7 +15691,7 @@
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -16095,7 +15715,7 @@
         <v>45779</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C98" s="1" t="n">
         <v>-15</v>
@@ -16106,7 +15726,7 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -16130,7 +15750,7 @@
         <v>45780</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>-500</v>
@@ -16139,11 +15759,11 @@
         <v>153</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -16167,7 +15787,7 @@
         <v>45785</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>-15</v>
@@ -16178,7 +15798,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
@@ -16202,7 +15822,7 @@
         <v>45788</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>-31180</v>
@@ -16215,7 +15835,7 @@
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
@@ -16239,7 +15859,7 @@
         <v>45796</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>-15</v>
@@ -16250,7 +15870,7 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
@@ -16274,7 +15894,7 @@
         <v>45796</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C103" s="1" t="n">
         <v>-2092</v>
@@ -16287,7 +15907,7 @@
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
@@ -16311,7 +15931,7 @@
         <v>45799</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>-15</v>
@@ -16322,7 +15942,7 @@
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
@@ -16346,7 +15966,7 @@
         <v>45799</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>-2440</v>
@@ -16359,7 +15979,7 @@
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
@@ -16383,7 +16003,7 @@
         <v>45803</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>-15</v>
@@ -16394,7 +16014,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
@@ -16418,7 +16038,7 @@
         <v>45805</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>-15</v>
@@ -16429,7 +16049,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
@@ -16453,7 +16073,7 @@
         <v>45808</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>-15</v>
@@ -16464,7 +16084,7 @@
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
@@ -16488,7 +16108,7 @@
         <v>45811</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>-15</v>
@@ -16499,7 +16119,7 @@
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
@@ -16523,7 +16143,7 @@
         <v>45815</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>-15</v>
@@ -16534,7 +16154,7 @@
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
@@ -16558,7 +16178,7 @@
         <v>45815</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>-8800</v>
@@ -16571,7 +16191,7 @@
       </c>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
@@ -16595,7 +16215,7 @@
         <v>45818</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>-15</v>
@@ -16606,7 +16226,7 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
@@ -16630,7 +16250,7 @@
         <v>45819</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C113" s="1" t="n">
         <v>-15</v>
@@ -16641,7 +16261,7 @@
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
@@ -16665,7 +16285,7 @@
         <v>45819</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>-35220</v>
@@ -16678,7 +16298,7 @@
       </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
@@ -16702,7 +16322,7 @@
         <v>45819</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>-50000</v>
@@ -16715,7 +16335,7 @@
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -16739,7 +16359,7 @@
         <v>45820</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>-15</v>
@@ -16750,7 +16370,7 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -16774,7 +16394,7 @@
         <v>45821</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>-15</v>
@@ -16785,7 +16405,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -16809,7 +16429,7 @@
         <v>45829</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C118" s="1" t="n">
         <v>-10</v>
@@ -16820,7 +16440,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -16844,7 +16464,7 @@
         <v>45829</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>-800</v>
@@ -16857,7 +16477,7 @@
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -16881,7 +16501,7 @@
         <v>45830</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>-15</v>
@@ -16892,7 +16512,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -16929,7 +16549,7 @@
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -16966,7 +16586,7 @@
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -16990,7 +16610,7 @@
         <v>45834</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C123" s="1" t="n">
         <v>-15</v>
@@ -17001,7 +16621,7 @@
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -17025,7 +16645,7 @@
         <v>45834</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C124" s="1" t="n">
         <v>-1500</v>
@@ -17038,7 +16658,7 @@
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -17062,7 +16682,7 @@
         <v>45841</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C125" s="1" t="n">
         <v>-5</v>
@@ -17073,7 +16693,7 @@
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -17097,7 +16717,7 @@
         <v>45841</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C126" s="1" t="n">
         <v>-2000</v>
@@ -17108,7 +16728,7 @@
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -17132,7 +16752,7 @@
         <v>45841</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C127" s="1" t="n">
         <v>-15</v>
@@ -17143,7 +16763,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -17167,7 +16787,7 @@
         <v>45843</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C128" s="1" t="n">
         <v>15</v>
@@ -17178,7 +16798,7 @@
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -17202,7 +16822,7 @@
         <v>45843</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C129" s="1" t="n">
         <v>-15</v>
@@ -17213,7 +16833,7 @@
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
@@ -17237,7 +16857,7 @@
         <v>45845</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C130" s="1" t="n">
         <v>-15</v>
@@ -17248,7 +16868,7 @@
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
@@ -17272,7 +16892,7 @@
         <v>45845</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C131" s="1" t="n">
         <v>-20000</v>
@@ -17285,7 +16905,7 @@
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
@@ -17309,7 +16929,7 @@
         <v>45846</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C132" s="1" t="n">
         <v>-15</v>
@@ -17320,7 +16940,7 @@
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
@@ -17344,7 +16964,7 @@
         <v>45847</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C133" s="1" t="n">
         <v>-15</v>
@@ -17355,7 +16975,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
@@ -17379,7 +16999,7 @@
         <v>45850</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C134" s="1" t="n">
         <v>-15</v>
@@ -17390,7 +17010,7 @@
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
@@ -17414,7 +17034,7 @@
         <v>45851</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C135" s="1" t="n">
         <v>-15</v>
@@ -17425,7 +17045,7 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
@@ -17449,7 +17069,7 @@
         <v>45852</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C136" s="1" t="n">
         <v>-5</v>
@@ -17460,7 +17080,7 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
@@ -17484,7 +17104,7 @@
         <v>45853</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C137" s="1" t="n">
         <v>-15</v>
@@ -17495,7 +17115,7 @@
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -17519,7 +17139,7 @@
         <v>45853</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C138" s="1" t="n">
         <v>-1200</v>
@@ -17532,7 +17152,7 @@
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
@@ -17556,7 +17176,7 @@
         <v>45857</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C139" s="1" t="n">
         <v>-5</v>
@@ -17567,7 +17187,7 @@
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
@@ -17591,7 +17211,7 @@
         <v>45857</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C140" s="1" t="n">
         <v>-2000</v>
@@ -17602,7 +17222,7 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -17626,7 +17246,7 @@
         <v>45859</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C141" s="1" t="n">
         <v>-15</v>
@@ -17637,7 +17257,7 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
@@ -17661,7 +17281,7 @@
         <v>45859</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C142" s="1" t="n">
         <v>-9918</v>
@@ -17670,11 +17290,11 @@
         <v>153</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
@@ -17698,7 +17318,7 @@
         <v>45863</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C143" s="1" t="n">
         <v>-15</v>
@@ -17709,7 +17329,7 @@
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
@@ -17733,7 +17353,7 @@
         <v>45867</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C144" s="1" t="n">
         <v>-6000</v>
@@ -17744,7 +17364,7 @@
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
@@ -17768,7 +17388,7 @@
         <v>45870</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C145" s="1" t="n">
         <v>-15</v>
@@ -17779,7 +17399,7 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
@@ -17803,7 +17423,7 @@
         <v>45873</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C146" s="1" t="n">
         <v>-15</v>
@@ -17814,7 +17434,7 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
@@ -17838,18 +17458,18 @@
         <v>45877</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C147" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H147" s="1" t="n">
         <v>2025</v>
@@ -17881,7 +17501,7 @@
         <v>45878</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C148" s="1" t="n">
         <v>-15</v>
@@ -17892,7 +17512,7 @@
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -17916,7 +17536,7 @@
         <v>45881</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C149" s="1" t="n">
         <v>-5</v>
@@ -17927,7 +17547,7 @@
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -17951,7 +17571,7 @@
         <v>45881</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C150" s="1" t="n">
         <v>-2000</v>
@@ -17962,7 +17582,7 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -17986,7 +17606,7 @@
         <v>45884</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C151" s="1" t="n">
         <v>-15</v>
@@ -17997,7 +17617,7 @@
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -18021,7 +17641,7 @@
         <v>45891</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C152" s="1" t="n">
         <v>-15</v>
@@ -18032,7 +17652,7 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -18056,7 +17676,7 @@
         <v>45891</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C153" s="1" t="n">
         <v>-4500</v>
@@ -18069,7 +17689,7 @@
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -18093,7 +17713,7 @@
         <v>45891</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C154" s="1" t="n">
         <v>-2440</v>
@@ -18106,7 +17726,7 @@
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -18130,7 +17750,7 @@
         <v>45896</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C155" s="1" t="n">
         <v>-10</v>
@@ -18141,7 +17761,7 @@
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -18165,7 +17785,7 @@
         <v>45896</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>-1000</v>
@@ -18174,11 +17794,11 @@
         <v>153</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -18202,7 +17822,7 @@
         <v>45897</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C157" s="1" t="n">
         <v>-15</v>
@@ -18213,7 +17833,7 @@
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -18237,7 +17857,7 @@
         <v>45901</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>-15</v>
@@ -18248,7 +17868,7 @@
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
@@ -18272,7 +17892,7 @@
         <v>45908</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>-15</v>
@@ -18283,7 +17903,7 @@
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
@@ -18307,18 +17927,18 @@
         <v>45910</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C160" s="1" t="n">
         <v>-588</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H160" s="1" t="n">
         <v>2025</v>
@@ -18350,7 +17970,7 @@
         <v>45912</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C161" s="1" t="n">
         <v>-15</v>
@@ -18361,7 +17981,7 @@
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
@@ -18385,7 +18005,7 @@
         <v>45913</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C162" s="1" t="n">
         <v>-5</v>
@@ -18396,7 +18016,7 @@
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
@@ -18420,7 +18040,7 @@
         <v>45913</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C163" s="1" t="n">
         <v>-2000</v>
@@ -18431,7 +18051,7 @@
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
@@ -18455,7 +18075,7 @@
         <v>45919</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C164" s="1" t="n">
         <v>-15</v>
@@ -18466,7 +18086,7 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
@@ -18490,7 +18110,7 @@
         <v>45922</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C165" s="1" t="n">
         <v>-15</v>
@@ -18501,7 +18121,7 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
@@ -18525,7 +18145,7 @@
         <v>45924</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C166" s="1" t="n">
         <v>-15</v>
@@ -18536,7 +18156,7 @@
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
@@ -18560,7 +18180,7 @@
         <v>45931</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C167" s="1" t="n">
         <v>-500</v>
@@ -18571,7 +18191,7 @@
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
@@ -18595,7 +18215,7 @@
         <v>45931</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C168" s="1" t="n">
         <v>-15</v>
@@ -18606,7 +18226,7 @@
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
@@ -18630,7 +18250,7 @@
         <v>45932</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C169" s="1" t="n">
         <v>-15</v>
@@ -18641,7 +18261,7 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
@@ -18665,7 +18285,7 @@
         <v>45932</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C170" s="1" t="n">
         <v>-6040</v>
@@ -18678,7 +18298,7 @@
       </c>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
@@ -18702,7 +18322,7 @@
         <v>45933</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C171" s="1" t="n">
         <v>-10</v>
@@ -18713,7 +18333,7 @@
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
@@ -18737,7 +18357,7 @@
         <v>45934</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C172" s="1" t="n">
         <v>-15</v>
@@ -18748,7 +18368,7 @@
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
@@ -18772,7 +18392,7 @@
         <v>45934</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C173" s="1" t="n">
         <v>-47000</v>
@@ -18785,7 +18405,7 @@
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
@@ -18809,7 +18429,7 @@
         <v>45934</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C174" s="1" t="n">
         <v>-50000</v>
@@ -18822,7 +18442,7 @@
       </c>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -18846,7 +18466,7 @@
         <v>45936</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="n">
         <v>-381</v>
@@ -18859,7 +18479,7 @@
       </c>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
@@ -18883,7 +18503,7 @@
         <v>45936</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C176" s="1" t="n">
         <v>-381</v>
@@ -18896,7 +18516,7 @@
       </c>
       <c r="F176" s="1"/>
       <c r="G176" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -18920,7 +18540,7 @@
         <v>45937</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C177" s="1" t="n">
         <v>-15</v>
@@ -18931,7 +18551,7 @@
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -18955,18 +18575,18 @@
         <v>45937</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C178" s="1" t="n">
         <v>-1592</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H178" s="1" t="n">
         <v>2025</v>
@@ -18998,18 +18618,18 @@
         <v>45937</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C179" s="1" t="n">
         <v>2388</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H179" s="1" t="n">
         <v>2025</v>
@@ -19041,18 +18661,18 @@
         <v>45937</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C180" s="1" t="n">
         <v>-796</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H180" s="1" t="n">
         <v>2025</v>
@@ -19084,7 +18704,7 @@
         <v>45938</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C181" s="1" t="n">
         <v>-15</v>
@@ -19095,7 +18715,7 @@
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -19119,7 +18739,7 @@
         <v>45940</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C182" s="1" t="n">
         <v>-15</v>
@@ -19130,7 +18750,7 @@
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -19167,7 +18787,7 @@
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -19191,7 +18811,7 @@
         <v>45941</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C184" s="1" t="n">
         <v>-15</v>
@@ -19202,7 +18822,7 @@
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -19226,18 +18846,18 @@
         <v>45942</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C185" s="1" t="n">
         <v>-4709</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H185" s="1" t="n">
         <v>2025</v>
@@ -19269,18 +18889,18 @@
         <v>45942</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C186" s="1" t="n">
         <v>-6215</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H186" s="1" t="n">
         <v>2025</v>
@@ -19312,18 +18932,18 @@
         <v>45942</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C187" s="1" t="n">
         <v>-2680</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H187" s="1" t="n">
         <v>2025</v>
@@ -19355,7 +18975,7 @@
         <v>45943</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C188" s="1" t="n">
         <v>-15</v>
@@ -19366,7 +18986,7 @@
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
@@ -19390,7 +19010,7 @@
         <v>45943</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C189" s="1" t="n">
         <v>-23120</v>
@@ -19403,7 +19023,7 @@
       </c>
       <c r="F189" s="1"/>
       <c r="G189" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
@@ -19427,18 +19047,18 @@
         <v>45943</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C190" s="1" t="n">
         <v>-6190</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H190" s="1" t="n">
         <v>2025</v>
@@ -19470,18 +19090,18 @@
         <v>45943</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C191" s="1" t="n">
         <v>-3211</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H191" s="1" t="n">
         <v>2025</v>
@@ -19513,18 +19133,18 @@
         <v>45944</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C192" s="1" t="n">
         <v>-3333</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H192" s="1" t="n">
         <v>2025</v>
@@ -19556,18 +19176,18 @@
         <v>45944</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C193" s="1" t="n">
         <v>-3333</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H193" s="1" t="n">
         <v>2025</v>
@@ -19599,18 +19219,18 @@
         <v>45944</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C194" s="1" t="n">
         <v>-3333</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H194" s="1" t="n">
         <v>2025</v>
@@ -19642,18 +19262,18 @@
         <v>45944</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C195" s="1" t="n">
         <v>6215</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H195" s="1" t="n">
         <v>2025</v>
@@ -19685,7 +19305,7 @@
         <v>45948</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C196" s="1" t="n">
         <v>-15</v>
@@ -19696,7 +19316,7 @@
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
@@ -19720,7 +19340,7 @@
         <v>45948</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C197" s="1" t="n">
         <v>-1500</v>
@@ -19733,7 +19353,7 @@
       </c>
       <c r="F197" s="1"/>
       <c r="G197" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
@@ -19757,7 +19377,7 @@
         <v>45948</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C198" s="1" t="n">
         <v>-1500</v>
@@ -19770,7 +19390,7 @@
       </c>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
@@ -19794,18 +19414,18 @@
         <v>45949</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C199" s="1" t="n">
         <v>-4758</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H199" s="1" t="n">
         <v>2025</v>
@@ -19837,18 +19457,18 @@
         <v>45949</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C200" s="1" t="n">
         <v>-926</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H200" s="1" t="n">
         <v>2025</v>
@@ -19880,7 +19500,7 @@
         <v>45952</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C201" s="1" t="n">
         <v>-15</v>
@@ -19891,7 +19511,7 @@
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
@@ -19915,18 +19535,18 @@
         <v>45957</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C202" s="1" t="n">
         <v>1598</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H202" s="1" t="n">
         <v>2025</v>
@@ -19958,18 +19578,18 @@
         <v>45957</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C203" s="1" t="n">
         <v>-1898</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H203" s="1" t="n">
         <v>2025</v>
@@ -20001,7 +19621,7 @@
         <v>45958</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C204" s="1" t="n">
         <v>-15</v>
@@ -20012,7 +19632,7 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H204" s="1"/>
       <c r="I204" s="1"/>
@@ -20036,18 +19656,18 @@
         <v>45961</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C205" s="1" t="n">
         <v>-9918</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H205" s="1" t="n">
         <v>2025</v>
@@ -20079,7 +19699,7 @@
         <v>45962</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C206" s="1" t="n">
         <v>-15</v>
@@ -20090,7 +19710,7 @@
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -20114,7 +19734,7 @@
         <v>45962</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C207" s="1" t="n">
         <v>-3140</v>
@@ -20127,7 +19747,7 @@
       </c>
       <c r="F207" s="1"/>
       <c r="G207" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -20151,7 +19771,7 @@
         <v>45962</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C208" s="1" t="n">
         <v>-3140</v>
@@ -20164,7 +19784,7 @@
       </c>
       <c r="F208" s="1"/>
       <c r="G208" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -20188,7 +19808,7 @@
         <v>45965</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C209" s="1" t="n">
         <v>-10</v>
@@ -20199,7 +19819,7 @@
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -20223,7 +19843,7 @@
         <v>45965</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C210" s="1" t="n">
         <v>-1000</v>
@@ -20232,11 +19852,11 @@
         <v>153</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -20260,7 +19880,7 @@
         <v>45965</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C211" s="1" t="n">
         <v>-15</v>
@@ -20271,7 +19891,7 @@
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -20295,7 +19915,7 @@
         <v>45965</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C212" s="1" t="n">
         <v>-2000</v>
@@ -20306,7 +19926,7 @@
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -20330,18 +19950,18 @@
         <v>45965</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C213" s="1" t="n">
         <v>-300</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H213" s="1" t="n">
         <v>2025</v>
@@ -20373,7 +19993,7 @@
         <v>45967</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C214" s="1" t="n">
         <v>-1000</v>
@@ -20384,7 +20004,7 @@
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -20408,7 +20028,7 @@
         <v>45967</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C215" s="1" t="n">
         <v>-15</v>
@@ -20419,7 +20039,7 @@
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -20443,7 +20063,7 @@
         <v>45967</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C216" s="1" t="n">
         <v>-800</v>
@@ -20456,7 +20076,7 @@
       </c>
       <c r="F216" s="1"/>
       <c r="G216" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H216" s="1"/>
       <c r="I216" s="1"/>
@@ -20480,7 +20100,7 @@
         <v>45968</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C217" s="1" t="n">
         <v>-15</v>
@@ -20491,7 +20111,7 @@
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H217" s="1"/>
       <c r="I217" s="1"/>
@@ -20515,7 +20135,7 @@
         <v>45969</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C218" s="1" t="n">
         <v>-15</v>
@@ -20526,7 +20146,7 @@
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
@@ -20550,7 +20170,7 @@
         <v>45972</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C219" s="1" t="n">
         <v>25000</v>
@@ -20563,7 +20183,7 @@
         <v>215</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
@@ -20587,7 +20207,7 @@
         <v>45973</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C220" s="1" t="n">
         <v>-10</v>
@@ -20598,7 +20218,7 @@
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
@@ -20622,7 +20242,7 @@
         <v>45974</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C221" s="1" t="n">
         <v>-5</v>
@@ -20633,7 +20253,7 @@
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H221" s="1"/>
       <c r="I221" s="1"/>
@@ -20657,7 +20277,7 @@
         <v>45974</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C222" s="1" t="n">
         <v>-14000</v>
@@ -20670,7 +20290,7 @@
       </c>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H222" s="1"/>
       <c r="I222" s="1"/>
@@ -20694,7 +20314,7 @@
         <v>45975</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C223" s="1" t="n">
         <v>-5</v>
@@ -20705,7 +20325,7 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H223" s="1"/>
       <c r="I223" s="1"/>
@@ -20729,18 +20349,18 @@
         <v>45975</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C224" s="1" t="n">
         <v>-2196</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H224" s="1" t="n">
         <v>2025</v>
@@ -20772,18 +20392,18 @@
         <v>45975</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C225" s="1" t="n">
         <v>-29</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H225" s="1" t="n">
         <v>2025</v>
@@ -20815,18 +20435,18 @@
         <v>45975</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C226" s="1" t="n">
         <v>-6591</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H226" s="1" t="n">
         <v>2025</v>
@@ -20858,7 +20478,7 @@
         <v>45977</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C227" s="1" t="n">
         <v>-15</v>
@@ -20869,7 +20489,7 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H227" s="1"/>
       <c r="I227" s="1"/>
@@ -20893,18 +20513,18 @@
         <v>45977</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C228" s="1" t="n">
         <v>-326</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H228" s="1" t="n">
         <v>2025</v>
@@ -20936,18 +20556,18 @@
         <v>45979</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C229" s="1" t="n">
         <v>-470</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H229" s="1" t="n">
         <v>2025</v>
@@ -20979,18 +20599,18 @@
         <v>45980</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C230" s="1" t="n">
         <v>-1813</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H230" s="1" t="n">
         <v>2025</v>
@@ -21022,18 +20642,18 @@
         <v>45980</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C231" s="1" t="n">
         <v>-126</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H231" s="1" t="n">
         <v>2025</v>
@@ -21065,18 +20685,18 @@
         <v>45980</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C232" s="1" t="n">
         <v>-8391</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H232" s="1" t="n">
         <v>2025</v>
@@ -21108,18 +20728,18 @@
         <v>45981</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C233" s="1" t="n">
         <v>1813</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H233" s="1" t="n">
         <v>2025</v>
@@ -21151,18 +20771,18 @@
         <v>45981</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C234" s="1" t="n">
         <v>-5458</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H234" s="1" t="n">
         <v>2025</v>
@@ -21194,7 +20814,7 @@
         <v>45982</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C235" s="1" t="n">
         <v>-10</v>
@@ -21205,7 +20825,7 @@
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -21229,7 +20849,7 @@
         <v>45982</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C236" s="1" t="n">
         <v>-15</v>
@@ -21240,7 +20860,7 @@
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -21264,7 +20884,7 @@
         <v>45982</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C237" s="1" t="n">
         <v>-2440</v>
@@ -21277,7 +20897,7 @@
       </c>
       <c r="F237" s="1"/>
       <c r="G237" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -21301,18 +20921,18 @@
         <v>45982</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C238" s="1" t="n">
         <v>-2494</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H238" s="1" t="n">
         <v>2025</v>
@@ -21344,7 +20964,7 @@
         <v>45983</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C239" s="1" t="n">
         <v>-15</v>
@@ -21355,7 +20975,7 @@
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -21379,7 +20999,7 @@
         <v>45983</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C240" s="1" t="n">
         <v>-4400</v>
@@ -21388,11 +21008,11 @@
         <v>153</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F240" s="1"/>
       <c r="G240" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -21416,7 +21036,7 @@
         <v>45984</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C241" s="1" t="n">
         <v>-10</v>
@@ -21427,7 +21047,7 @@
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -21451,7 +21071,7 @@
         <v>45984</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C242" s="1" t="n">
         <v>-1000</v>
@@ -21460,11 +21080,11 @@
         <v>153</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F242" s="1"/>
       <c r="G242" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -21488,7 +21108,7 @@
         <v>45991</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C243" s="1" t="n">
         <v>-5</v>
@@ -21499,7 +21119,7 @@
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -21523,18 +21143,18 @@
         <v>45991</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C244" s="1" t="n">
         <v>-620</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H244" s="1" t="n">
         <v>2025</v>
@@ -21566,7 +21186,7 @@
         <v>45992</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C245" s="1" t="n">
         <v>-15</v>
@@ -21577,7 +21197,7 @@
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
@@ -21601,7 +21221,7 @@
         <v>45993</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C246" s="1" t="n">
         <v>-10</v>
@@ -21612,7 +21232,7 @@
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
@@ -21636,7 +21256,7 @@
         <v>45995</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C247" s="1" t="n">
         <v>-10</v>
@@ -21647,7 +21267,7 @@
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
@@ -21671,7 +21291,7 @@
         <v>45995</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C248" s="1" t="n">
         <v>-1000</v>
@@ -21682,7 +21302,7 @@
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
@@ -21706,7 +21326,7 @@
         <v>45997</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C249" s="1" t="n">
         <v>-15</v>
@@ -21717,7 +21337,7 @@
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
@@ -21741,18 +21361,18 @@
         <v>45997</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C250" s="1" t="n">
         <v>-1999</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H250" s="1" t="n">
         <v>2025</v>
@@ -21784,7 +21404,7 @@
         <v>45999</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C251" s="1" t="n">
         <v>-15</v>
@@ -21795,7 +21415,7 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H251" s="1"/>
       <c r="I251" s="1"/>
@@ -21819,7 +21439,7 @@
         <v>45999</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C252" s="1" t="n">
         <v>-16780</v>
@@ -21832,7 +21452,7 @@
       </c>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H252" s="1"/>
       <c r="I252" s="1"/>
@@ -21856,7 +21476,7 @@
         <v>46000</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C253" s="1" t="n">
         <v>-15</v>
@@ -21867,7 +21487,7 @@
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
@@ -21891,7 +21511,7 @@
         <v>46002</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C254" s="1" t="n">
         <v>-2000</v>
@@ -21904,7 +21524,7 @@
       </c>
       <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
@@ -21928,7 +21548,7 @@
         <v>46004</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C255" s="1" t="n">
         <v>-10</v>
@@ -21939,7 +21559,7 @@
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H255" s="1"/>
       <c r="I255" s="1"/>
@@ -21963,7 +21583,7 @@
         <v>46004</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C256" s="1" t="n">
         <v>-1000</v>
@@ -21972,11 +21592,11 @@
         <v>153</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H256" s="1"/>
       <c r="I256" s="1"/>
@@ -22000,18 +21620,18 @@
         <v>46004</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C257" s="1" t="n">
         <v>1999</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H257" s="1" t="n">
         <v>2025</v>
@@ -22043,7 +21663,7 @@
         <v>46006</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C258" s="1" t="n">
         <v>-15</v>
@@ -22054,7 +21674,7 @@
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
@@ -22078,7 +21698,7 @@
         <v>46006</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C259" s="1" t="n">
         <v>-400</v>
@@ -22087,11 +21707,11 @@
         <v>153</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F259" s="1"/>
       <c r="G259" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
@@ -22115,18 +21735,18 @@
         <v>46011</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C260" s="1" t="n">
         <v>-262</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H260" s="1" t="n">
         <v>2025</v>
@@ -22158,7 +21778,7 @@
         <v>46012</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C261" s="1" t="n">
         <v>-15</v>
@@ -22169,7 +21789,7 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
@@ -22193,7 +21813,7 @@
         <v>46012</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C262" s="1" t="n">
         <v>-4000</v>
@@ -22204,7 +21824,7 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
@@ -22228,7 +21848,7 @@
         <v>46013</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C263" s="1" t="n">
         <v>-15</v>
@@ -22239,7 +21859,7 @@
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -22263,7 +21883,7 @@
         <v>46013</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C264" s="1" t="n">
         <v>-2440</v>
@@ -22276,7 +21896,7 @@
       </c>
       <c r="F264" s="1"/>
       <c r="G264" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -22300,7 +21920,7 @@
         <v>46014</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C265" s="1" t="n">
         <v>-49700</v>
@@ -22313,7 +21933,7 @@
       </c>
       <c r="F265" s="1"/>
       <c r="G265" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -22337,18 +21957,18 @@
         <v>46014</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C266" s="1" t="n">
         <v>-639</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H266" s="1" t="n">
         <v>2025</v>
@@ -22380,18 +22000,18 @@
         <v>46016</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C267" s="1" t="n">
         <v>-1569</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H267" s="1" t="n">
         <v>2025</v>
@@ -22423,7 +22043,7 @@
         <v>46020</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C268" s="1" t="n">
         <v>-15</v>
@@ -22434,7 +22054,7 @@
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -22458,7 +22078,7 @@
         <v>46021</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C269" s="1" t="n">
         <v>-15</v>
@@ -22469,7 +22089,7 @@
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -22493,7 +22113,7 @@
         <v>46022</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C270" s="1" t="n">
         <v>-3000</v>
@@ -22506,7 +22126,7 @@
       </c>
       <c r="F270" s="1"/>
       <c r="G270" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -22530,7 +22150,7 @@
         <v>46024</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C271" s="1" t="n">
         <v>-15</v>
@@ -22541,7 +22161,7 @@
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -22565,7 +22185,7 @@
         <v>46025</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C272" s="1" t="n">
         <v>-15</v>
@@ -22576,7 +22196,7 @@
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -22600,7 +22220,7 @@
         <v>46025</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C273" s="1" t="n">
         <v>-50000</v>
@@ -22613,7 +22233,7 @@
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
@@ -22637,18 +22257,18 @@
         <v>46027</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C274" s="1" t="n">
         <v>-798</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H274" s="1" t="n">
         <v>2026</v>
@@ -22680,18 +22300,18 @@
         <v>46028</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C275" s="1" t="n">
         <v>-2999</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H275" s="1" t="n">
         <v>2026</v>
@@ -22723,7 +22343,7 @@
         <v>46029</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C276" s="1" t="n">
         <v>-15</v>
@@ -22734,7 +22354,7 @@
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H276" s="1"/>
       <c r="I276" s="1"/>
@@ -22758,7 +22378,7 @@
         <v>46030</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C277" s="1" t="n">
         <v>-15</v>
@@ -22769,7 +22389,7 @@
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H277" s="1"/>
       <c r="I277" s="1"/>
@@ -22793,7 +22413,7 @@
         <v>46030</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C278" s="1" t="n">
         <v>-1500</v>
@@ -22804,7 +22424,7 @@
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
@@ -22828,7 +22448,7 @@
         <v>46033</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C279" s="1" t="n">
         <v>-10</v>
@@ -22839,7 +22459,7 @@
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H279" s="1"/>
       <c r="I279" s="1"/>
@@ -22863,18 +22483,18 @@
         <v>46034</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C280" s="1" t="n">
         <v>-998</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H280" s="1" t="n">
         <v>2026</v>
@@ -22906,7 +22526,7 @@
         <v>46035</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C281" s="1" t="n">
         <v>-15</v>
@@ -22917,7 +22537,7 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H281" s="1"/>
       <c r="I281" s="1"/>
@@ -22941,7 +22561,7 @@
         <v>46035</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C282" s="1" t="n">
         <v>-37756</v>
@@ -22954,7 +22574,7 @@
       </c>
       <c r="F282" s="1"/>
       <c r="G282" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H282" s="1"/>
       <c r="I282" s="1"/>
@@ -22978,7 +22598,7 @@
         <v>46037</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C283" s="1" t="n">
         <v>-15</v>
@@ -22989,7 +22609,7 @@
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H283" s="1"/>
       <c r="I283" s="1"/>
@@ -23013,7 +22633,7 @@
         <v>46037</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C284" s="1" t="n">
         <v>-400</v>
@@ -23022,11 +22642,11 @@
         <v>153</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H284" s="1"/>
       <c r="I284" s="1"/>
@@ -23050,18 +22670,18 @@
         <v>46037</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C285" s="1" t="n">
         <v>-9918</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H285" s="1" t="n">
         <v>2026</v>
@@ -23093,18 +22713,18 @@
         <v>46038</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C286" s="1" t="n">
         <v>998</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H286" s="1" t="n">
         <v>2026</v>
@@ -23136,7 +22756,7 @@
         <v>46039</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C287" s="1" t="n">
         <v>-15</v>
@@ -23147,7 +22767,7 @@
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H287" s="1"/>
       <c r="I287" s="1"/>
@@ -23171,7 +22791,7 @@
         <v>46039</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C288" s="1" t="n">
         <v>-2410</v>
@@ -23184,7 +22804,7 @@
       </c>
       <c r="F288" s="1"/>
       <c r="G288" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H288" s="1"/>
       <c r="I288" s="1"/>
@@ -23208,7 +22828,7 @@
         <v>46047</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C289" s="1" t="n">
         <v>-500</v>
@@ -23219,7 +22839,7 @@
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H289" s="1"/>
       <c r="I289" s="1"/>
@@ -23243,7 +22863,7 @@
         <v>46047</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C290" s="1" t="n">
         <v>-15</v>
@@ -23254,7 +22874,7 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H290" s="1"/>
       <c r="I290" s="1"/>
@@ -23278,7 +22898,7 @@
         <v>46047</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C291" s="1" t="n">
         <v>-2440</v>
@@ -23291,7 +22911,7 @@
       </c>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H291" s="1"/>
       <c r="I291" s="1"/>
@@ -23315,18 +22935,18 @@
         <v>46053</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C292" s="1" t="n">
         <v>-552</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H292" s="1" t="n">
         <v>2026</v>
@@ -23358,7 +22978,7 @@
         <v>46054</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C293" s="1" t="n">
         <v>-15</v>
@@ -23369,7 +22989,7 @@
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -23393,7 +23013,7 @@
         <v>46055</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C294" s="1" t="n">
         <v>-5</v>
@@ -23404,7 +23024,7 @@
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -23428,7 +23048,7 @@
         <v>46058</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C295" s="1" t="n">
         <v>-15</v>
@@ -23439,7 +23059,7 @@
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -23463,7 +23083,7 @@
         <v>46059</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C296" s="1" t="n">
         <v>-10</v>
@@ -23474,7 +23094,7 @@
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -23498,18 +23118,18 @@
         <v>46059</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C297" s="1" t="n">
         <v>-4248</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H297" s="1" t="n">
         <v>2026</v>
@@ -23541,18 +23161,18 @@
         <v>46060</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C298" s="1" t="n">
         <v>552</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H298" s="1" t="n">
         <v>2026</v>
@@ -23584,7 +23204,7 @@
         <v>46062</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C299" s="1" t="n">
         <v>-15</v>
@@ -23595,7 +23215,7 @@
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -23619,7 +23239,7 @@
         <v>46066</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C300" s="1" t="n">
         <v>-5</v>
@@ -23630,7 +23250,7 @@
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -23654,7 +23274,7 @@
         <v>46066</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C301" s="1" t="n">
         <v>-5000</v>
@@ -23665,7 +23285,7 @@
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -23689,7 +23309,7 @@
         <v>46068</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C302" s="1" t="n">
         <v>-10</v>
@@ -23700,7 +23320,7 @@
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
@@ -23724,7 +23344,7 @@
         <v>46068</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C303" s="1" t="n">
         <v>-1000</v>
@@ -23735,7 +23355,7 @@
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="H303" s="1"/>
       <c r="I303" s="1"/>
@@ -23759,7 +23379,7 @@
         <v>46068</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C304" s="1" t="n">
         <v>-400</v>
@@ -23768,11 +23388,11 @@
         <v>153</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F304" s="1"/>
       <c r="G304" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H304" s="1"/>
       <c r="I304" s="1"/>
@@ -23796,7 +23416,7 @@
         <v>46069</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C305" s="1" t="n">
         <v>-15</v>
@@ -23807,7 +23427,7 @@
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H305" s="1"/>
       <c r="I305" s="1"/>
@@ -23839,7 +23459,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -23906,7 +23526,7 @@
         <v>45846</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>-18210</v>
@@ -23917,7 +23537,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -23949,7 +23569,7 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="79.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
@@ -24016,7 +23636,7 @@
         <v>45631</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>50000</v>
@@ -24026,10 +23646,10 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -24045,7 +23665,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3">
@@ -24053,7 +23673,7 @@
         <v>45631</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>50000</v>
@@ -24066,7 +23686,7 @@
         <v>192</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -24082,7 +23702,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4">
@@ -24090,7 +23710,7 @@
         <v>45653</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>50000</v>
@@ -24103,7 +23723,7 @@
         <v>215</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -24119,7 +23739,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5">
@@ -24127,7 +23747,7 @@
         <v>45654</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>50000</v>
@@ -24140,7 +23760,7 @@
         <v>192</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -24156,7 +23776,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6">
@@ -24164,7 +23784,7 @@
         <v>45656</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>50000</v>
@@ -24174,10 +23794,10 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -24193,7 +23813,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7">
@@ -24201,7 +23821,7 @@
         <v>45694</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>50000</v>
@@ -24214,7 +23834,7 @@
         <v>192</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -24230,7 +23850,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8">
@@ -24238,7 +23858,7 @@
         <v>45694</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>50000</v>
@@ -24248,10 +23868,10 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -24267,7 +23887,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -24275,7 +23895,7 @@
         <v>45694</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>50000</v>
@@ -24288,7 +23908,7 @@
         <v>215</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -24304,7 +23924,7 @@
         <v>3</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10">
@@ -24312,7 +23932,7 @@
         <v>45712</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>50000</v>
@@ -24325,7 +23945,7 @@
         <v>192</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -24341,7 +23961,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
@@ -24349,7 +23969,7 @@
         <v>45712</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>50000</v>
@@ -24362,7 +23982,7 @@
         <v>192</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -24378,7 +23998,7 @@
         <v>3</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12">
@@ -24386,7 +24006,7 @@
         <v>45759</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>47168</v>
@@ -24399,7 +24019,7 @@
         <v>192</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -24415,7 +24035,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13">
@@ -24436,7 +24056,7 @@
         <v>192</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -24452,7 +24072,7 @@
         <v>11</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14">
@@ -24460,7 +24080,7 @@
         <v>45934</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>73500</v>
@@ -24473,7 +24093,7 @@
         <v>192</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -24489,7 +24109,7 @@
         <v>11</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15">
@@ -24497,7 +24117,7 @@
         <v>45972</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>25000</v>
@@ -24510,7 +24130,7 @@
         <v>192</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -24526,7 +24146,7 @@
         <v>12</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
